--- a/Ministry_of_Public_Works_and_Transport.xlsx
+++ b/Ministry_of_Public_Works_and_Transport.xlsx
@@ -413,8 +413,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
@@ -484,6 +484,1775 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>قرار تعديل تعرفة أجور النقل من مطار رفيق الحريري الدولي - بيروت إلى كافة المناطق اللبنانية</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2025/June/قرار-تعديل-تعرفة-اجور-النقل-من-مطار-رفيق-الحريري-ا</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>03
+      تموز
+2025
+قرار تعديل تعرفة أجور النقل من مطار رفيق الحريري الدولي - بيروت إلى كافة المناطق اللبنانية</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:31:40.511054+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>إعلان الملتزم المؤقت للمزايدة العمومية - أشغال إزالة وشفط الرمول من الحوض المائي - العقيبة</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2025/MAY/اعلان-الملتزم-الموقت-للمزايدة-العمومية-اشغال-ازالة</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>إعلان الملتزم المؤقت للمزايدة العمومية - أشغال إزالة وشفط الرمول من الحوض المائي - العقيبة
+إعلان الملتزم المؤقت للمزايدة العمومية - أشغال إزالة وشفط الرمول من الحوض المائي - العقيبة
+اعلان-الملتزم-الموقت-للمزايدة-العمومية-اشغال-ازالة-وشفط-الرمول-من-الحوض-المايي-العقيبة.pdf</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:31:42.641512+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>إعلان الملتزم المؤقت للمزايدة العمومية - أشغال إزالة وشفط الرمول من الحوض المائي - صيدا</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2025/MAY/اعلان-الملتزم-الموقت-للمزايدة-العمومية-اشغال-ا-(1)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>إعلان الملتزم المؤقت للمزايدة العمومية - أشغال إزالة وشفط الرمول من الحوض المائي - صيدا
+إعلان الملتزم المؤقت للمزايدة العمومية - أشغال إزالة وشفط الرمول من الحوض المائي - صيدا
+اعلان-الملتزم-الموقت-للمزايدة-العمومية-اشغال-ازالة-وشفط-الرمول-من-الحوض-المايي-صيدا.pdf</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:31:44.746185+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>لائحة الوظائف المعلن عنها حاليّا في وزارة الأشغال العامة و النقل</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2025/MAY/لايحة-الوظايف-المعلن-عنها-حاليافي-في-وزارة-الاشغال</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>لائحة الوظائف المعلن عنها حاليّا في وزارة الأشغال العامة و النقل
+لائحة الوظائف المعلن عنها حاليّا: 
+-  رئيس مجلس إدارة مدير عام الهيئة العامة للطيران المدني 
+تفاصيل الوظيفة   MOPW006_manager.pdf    
+للترشيح  
+- عضو مجلس إدارة الهيئة العامة للطيران المدني 
+تفاصيل الوظيفة    MOPW007_member.pdf   
+للترشيح  
+- مفوض حكومة لدى الهيئة العامة للطيران المدني
+تفاصيل الوظيفة   MOPW008_commissioner.pdf   
+للترشيح</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:31:46.988440+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق في قضاء عكار</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/September/دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تا-(10)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>18 أيلول 2024 دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق في قضاء عكار دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق في قضاء عكار دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-طريق-في-قضاء-عكار.pdf</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:31:49.200664+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 9 طرق في قضاء عكار</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/September/قرار-رقم-593-اعلان-الملتزم-الموقت-لاشغال-تاهيل-وصي</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>18 أيلول 2024 دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 9 طرق في قضاء عكار دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 9 طرق في قضاء عكار دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-9-طرق-في-قضاء-عكار.pdf</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:31:51.343238+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 7 طرق في قضاء المتن</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/September/دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاه-(4)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>06 أيلول 2024 دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 7 طرق في قضاء المتن دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 7 طرق في قضاء المتن دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-7-طرق-في-قضاء-المتن-(1).pdf</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:31:53.581772+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق في قضاء الشوف</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/September/دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاه-(5)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>06 أيلول 2024 دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق في قضاء الشوف دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق في قضاء الشوف دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-طريق-في-قضاء-الشوف.pdf</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:31:55.671960+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 10طرق في قضاء الشوف</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/September/دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاه-(6)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>06 أيلول 2024 دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 10طرق في قضاء الشوف دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 10طرق في قضاء الشوف دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-10طرق-في-قضاء-الشوف.pdf</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:31:57.784554+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق في قضاء المنية الضنية</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/September/دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاه-(7)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق في قضاء المنية الضنية
+دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق في قضاء المنية الضنية
+دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-طريق-في-قضاء-المنية-الضنية.pdf</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:31:59.895213+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريقين في قضاء زحلة</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/September/دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاه-(8)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>06 أيلول 2024 دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريقين في قضاء زحلة دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريقين في قضاء زحلة دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-طريقين-في-قضاء-زحلة.pdf</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:32:04.161833+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 7 طرق في قضاء حاصبيا</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/September/دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-و</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>04 أيلول 2024 دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 7 طرق في قضاء حاصبيا دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 7 طرق في قضاء حاصبيا دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-7-طرق-في-قضاء-حاصبيا.pdf</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:32:06.279689+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 15 طريق في قضاء الهرمل</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/September/دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاه-(1)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>04 أيلول 2024 دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 15 طريق في قضاء الهرمل دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 15 طريق في قضاء الهرمل دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-15-طريق-في-قضاء-الهرمل.pdf</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:32:08.408362+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق الحازمية - جسر الباشا قضاء بعبدا</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/September/دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاه-(2)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق الحازمية - جسر الباشا قضاء بعبدا
+دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق الحازمية - جسر الباشا قضاء بعبدا
+دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-طريق-الحازمية-جسر-الباشا-قضاء-بعبدا.pdf</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:32:10.640872+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق عرمان - المنية - المخيم في المنية</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/September/دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاه-(3)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق عرمان - المنية - المخيم في المنية
+دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق عرمان - المنية - المخيم في المنية
+دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-طريق-عرمان-المنية-المخيم-في-المنية.pdf</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:32:12.734560+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>قرار رقم 531 إعلان الملتزم المؤقت لأشغال تأهيل وصيانة بعض أقسام شبكة الطرق</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/August/قرار-رقم-531-اعلان-الملتزم-الموقت-لاشغال-تاهيل-وصي</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>20 آب 2024 قرار رقم 531 إعلان الملتزم المؤقت لأشغال تأهيل وصيانة بعض أقسام شبكة الطرق قرار رقم 531 إعلان الملتزم المؤقت لأشغال تأهيل وصيانة بعض أقسام شبكة الطرق قرار-رقم-531-اعلان-الملتزم-الموقت-لاشغال-تاهيل-وصيانة-بعض-اقسام-شبكة-الطرق.pdf</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:32:14.923843+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>قرار 492 إعلان الملتزم المؤقت لأشغال ملفات تلزيم صيانة بعض أقسام شبكة الطرق</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/August/قرار-492-اعلان-الملتزم-الموقت-لاشغال-ملفات-تلزيم-ص</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>08 آب 2024 قرار 492 إعلان الملتزم المؤقت لأشغال ملفات تلزيم صيانة بعض أقسام شبكة الطرق قرار 492 إعلان الملتزم المؤقت لأشغال ملفات تلزيم صيانة بعض أقسام شبكة الطرق قرار-492-اعلان-الملتزم-الموقت-لاشغال-ملفات-تلزيم-صيانة-بعض-اقسام-شبكة-الطرق-(1).pdf</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:32:17.062927+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>قرار 493 إعلان الملتزم المؤقت لأشغال ملفات تلزيم صيانة بعض أقسام شبكة الطرق</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/August/قرار-493-اعلان-الملتزم-الموقت-لاشغال-ملفات-تلزيم-ص</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>08 آب 2024 قرار 493 إعلان الملتزم المؤقت لأشغال ملفات تلزيم صيانة بعض أقسام شبكة الطرق قرار 493 إعلان الملتزم المؤقت لأشغال ملفات تلزيم صيانة بعض أقسام شبكة الطرق قرار-493-اعلان-الملتزم-الموقت-لاشغال-ملفات-تلزيم-صيانة-بعض-اقسام-شبكة-الطرق-(1).pdf</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:32:19.180338+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 8 طرق في قضاء زحلة</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/August/دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-و</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>07 آب 2024 دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 8 طرق في قضاء زحلة دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 8 طرق في قضاء زحلة دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-8-طرق-في-قضاء-زحلة.pdf</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:32:21.286615+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 4 طرق في قضاء عكار</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/August/دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاه-(1)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>07 آب 2024 دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 4 طرق في قضاء عكار دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 4 طرق في قضاء عكار دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-4-طرق-في-قضاء-عكار.pdf</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:32:23.388530+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 6 طرق في قضاء زحلة</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/August/دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاه-(2)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>07 آب 2024 دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 6 طرق في قضاء زحلة دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 6 طرق في قضاء زحلة دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-6-طرق-في-قضاء-زحلة.pdf</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:32:27.613678+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 15 طريق في قضاء بعلبك</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/August/دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاه-(3)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>07 آب 2024 دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 15 طريق في قضاء بعلبك دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة 15 طريق في قضاء بعلبك دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-15-طريق-في-قضاء-بعلبك.pdf</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:32:29.717472+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق في قضاء المتن</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/August/دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاه-(4)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>07 آب 2024 دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق في قضاء المتن دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق في قضاء المتن دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-طريق-في-قضاء-المتن.pdf</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:32:31.820520+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>دعوة للإعلان عن مناقصة عمومية لتلزيم تأمين تقديم زيوت فلاتر بطاريات، إطارات مطاطية لآليات</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/August/دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-تامين-تقديم-ز</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>دعوة للإعلان عن مناقصة عمومية لتلزيم تأمين تقديم زيوت فلاتر بطاريات، إطارات مطاطية لآليات
+دعوة للإعلان عن مناقصة عمومية لتلزيم تأمين تقديم زيوت فلاتر بطاريات، إطارات مطاطية لآليات
+دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-تامين-تقديم-زيوت-فلاتر-بطاريات،-اطارات-مطاطية-لاليات.pdf</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:32:33.912249+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>دعوة للإعلان عن مناقصة عمومية لتلزيم تقديم وتركيب قطع غيار لزوم صيانة وتشغيل آليات رفع الثلوج</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/August/دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-تقديم-وتركيب</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>دعوة للإعلان عن مناقصة عمومية لتلزيم تقديم وتركيب قطع غيار لزوم صيانة وتشغيل آليات رفع الثلوج
+دعوة للإعلان عن مناقصة عمومية لتلزيم تقديم وتركيب قطع غيار لزوم صيانة وتشغيل آليات رفع الثلوج
+دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-تقديم-وتركيب-قطع-غيار-لزوم-صيانة-وتشغيل.pdf</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:32:36.020371+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>دعوة للاعلان عن أشغال تلزيم صيانة طريق دير المخلص - طريق المصانع في قضاء الشوف</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/July/دعوة-للاعلان-عن-اشغال-تلزيم-صيانة-طريق-دير-المخلص</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>دعوة للاعلان عن أشغال تلزيم صيانة طريق دير المخلص - طريق المصانع في قضاء الشوف
+دعوة للاعلان عن أشغال تلزيم صيانة طريق دير المخلص - طريق المصانع في قضاء الشوف
+قرار-رقم-477-اعلان-الملتزم-الموقت-لاشغال-تلزيم-صيانة-طريق-دير-المخلص-طريق-المصانع-في-قضاء-الشوف.pdf</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:32:38.143931+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>دعوة للاعلان عن أشغال ملفات تلزيم صيانة بعض أقسام شبكة الطرق</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/July/دعوة-للاعلان-عن-اشغال-ملفات-تلزيم-صيانة-بعض-اقسام</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>29 تموز 2024 دعوة للاعلان عن أشغال ملفات تلزيم صيانة بعض أقسام شبكة الطرق دعوة للاعلان عن أشغال ملفات تلزيم صيانة بعض أقسام شبكة الطرق قرار-رقم-475-اعلان-الملتزم-الموقت-لاشغال-ملفات-تلزيم-صيانة-بعض-اقسام-شبكة-الطرق.pdf</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:32:40.296604+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>دعوة للاعلان عن أشغال ملفات تلزيم صيانة بعض أقسام شبكة الطرق بطريقة عروض الأسعار</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/July/دعوة-للاعلان-عن-اشغال-ملفات-تلزيم-صيانة-بعض-اق-(1)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>29 تموز 2024 دعوة للاعلان عن أشغال ملفات تلزيم صيانة بعض أقسام شبكة الطرق بطريقة عروض الأسعار دعوة للاعلان عن أشغال ملفات تلزيم صيانة بعض أقسام شبكة الطرق بطريقة عروض الأسعار قرار-رقم-478-اعلان-الملتزم-الموقت-لاشغال-ملفات-تلزيم-صيانة-بعض-اقسام-شبكة-الطرق_.pdf</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:32:42.537681+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>تخفيض مهلة الإعلان عن المناقصات العمومية لأشغال صيانة وتأهيل بعض أقسام شبكة الطرق</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/July/تخفيض-مهلة-الاعلان-عن-المناقصات-العمومية-لاشغال-صي</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>29
+      تموز
+2024
+تخفيض مهلة الإعلان عن المناقصات العمومية لأشغال صيانة وتأهيل بعض أقسام شبكة الطرق
+تخفيض مهلة الإعلان عن المناقصات العمومية لأشغال صيانة وتأهيل بعض أقسام شبكة الطرققرار-رقم-476-تخفيض-مهلة-الاعلان-عن-المناقصات-العمومية-لاشغال-صيانة-وتاهيل-بعض-اقسام-شبكة-الطرق.pdf</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:32:44.628176+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق الحازمية-جسر الباشا في قضاء بعبدا</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/July/دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-و</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>29
+      تموز
+2024
+دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق الحازمية-جسر الباشا في قضاء بعبدا
+دعوة للإعلان عن مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق الحازمية-جسر الباشا في قضاء بعبدادعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-طريق-الحازمية-جسر-الباشا-في-قضاء-بعبدا.pdf</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:32:46.839916+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>مناقصة عامة علنية لتلزيم أشغال ضرورية وملحة في مبنى قائمقامية المتن</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/June/مناقصة-عامة-علنية-لتلزيم-اشغال-ضرورية-وملحة-في-مبن</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>26 حزيران 2024 مناقصة عامة علنية لتلزيم أشغال ضرورية وملحة في مبنى قائمقامية المتن مناقصة عامة علنية لتلزيم أشغال ضرورية وملحة في مبنى قائمقامية المتن دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-ضرورية-وملحة-في-مبنى-قايمقامية-المتن-(1).pdf</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:32:51.141908+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>مناقصة أشغال تأهيل وصيانة طرق: 1-طريق وقناة المسيل الصويري / 2- دار الحنان - الصويري -جبانة المجدل /</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/June/مناقصة-اشغال-تاهيل-وصيانة-طرق-1-طريق-وقناة-المسيل</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>مناقصة أشغال تأهيل وصيانة طرق: 1-طريق وقناة المسيل الصويري / 2- دار الحنان - الصويري -جبانة المجدل / 3-جبانة الصويري / 4- ثانوية الصويري في قضاء البقاع الغربي.
+مناقصة أشغال تأهيل وصيانة طرق: 1-طريق وقناة المسيل الصويري / 2- دار الحنان - الصويري -جبانة المجدل / 3-جبانة الصويري / 4- ثانوية الصويري في قضاء البقاع الغربي.
+دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-4-طرق-في-قضاء-البقاع-الغربي-(1).pdf</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:32:53.265087+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>مناقصة عامة علنية لتلزيم أشغال ضرورية وملحة في مبنى قصر عدل النبطية</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/June/مناقصة-عامة-علنية-لتلزيم-اشغال-ضرورية-وملحة-في-(1)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>26 حزيران 2024 مناقصة عامة علنية لتلزيم أشغال ضرورية وملحة في مبنى قصر عدل النبطية مناقصة عامة علنية لتلزيم أشغال ضرورية وملحة في مبنى قصر عدل النبطية دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-ضرورية-وملحة-في-قصر-عدل-النبطية.pdf</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:32:55.380432+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طرق:1- زغرتا - اهدن - بشري / 2- مفرق مجدليا - مجدليا / 3- ال</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/June/مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-طرق-1-زغرت</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طرق:1- زغرتا - اهدن - بشري / 2- مفرق مجدليا - مجدليا / 3- البداوي - مجدليا / 4- بيادر رشعين زغرتا / 5- حرف اردة - بيادر رشعين / 6- مفرق الخالدية - صخرا- بشحار / 7- زغرتا - اصنون / 8- مفرق قرباش - قرباش / 9- مفرق حصرون الجديدة - حصرون الجديدة / 10- اصنون - قرباش / 11- طريق كرم سدة – سرعل في قضاء زغرتا
+مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طرق:1- زغرتا - اهدن - بشري / 2- مفرق مجدليا - مجدليا / 3- البداوي - مجدليا / 4- بيادر رشعين زغرتا / 5- حرف اردة - بيادر رشعين / 6- مفرق الخالدية - صخرا- بشحار / 7- زغرتا - اصنون / 8- مفرق قرباش - قرباش / 9- مفرق حصرون الجديدة - حصرون الجديدة / 10- اصنون - قرباش / 11- طريق كرم سدة – سرعل في قضاء زغرتا
+دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-11-طريق-في-قضاء-زغرتا.pdf</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:32:57.623983+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق: حي الصوانة- كسار المشرقي- طريق الخزان في علمات في قضاء</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/June/مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-طريق-حي-ال</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق: حي الصوانة- كسار المشرقي- طريق الخزان في علمات في قضاء جبيل
+مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق: حي الصوانة- كسار المشرقي- طريق الخزان في علمات في قضاء جبيل
+دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-طريق-في-قضاء-جبيل.pdf</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:32:59.702263+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق: القناة- لالا- بعلول- القرعون في قضاء البقاع الغربي</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/June/مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-طريق-القنا</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق: القناة- لالا- بعلول- القرعون في قضاء البقاع الغربي
+مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق: القناة- لالا- بعلول- القرعون في قضاء البقاع الغربي
+دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-طريق-في-قضاء-البقاع-الغربي.pdf</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:33:01.812929+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طرق:1- كفريا - جب جنين / 2- مقابر المسيحيين - المخابرات جب ج</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/June/مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-طرق-1-كفري</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طرق:1- كفريا - جب جنين / 2- مقابر المسيحيين - المخابرات جب جنين في قضاء البقاع الغربي
+مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طرق:1- كفريا - جب جنين / 2- مقابر المسيحيين - المخابرات جب جنين في قضاء البقاع الغربي
+دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-طريقين-في-البقاع-الغربي.pdf</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:33:03.917512+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طرق: 1- حي الدسوقي - جب جنين / 2- داخلي في المنصورة / 3- مط</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/June/مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-طرق-1-حي-ا</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طرق: 1- حي الدسوقي - جب جنين / 2- داخلي في المنصورة / 3- مطعم السبع عيون - القاعة خربة قانافار في قضاء البقاع الغربي
+مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طرق: 1- حي الدسوقي - جب جنين / 2- داخلي في المنصورة / 3-  مطعم السبع عيون - القاعة خربة قانافار في
+قضاء البقاع الغربي
+دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-3-طرق-في-قضاء-البقاع-الغربي.pdf</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:33:06.140444+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طرق: 1- بطرماز- بيت حاويك / 2- قرحيا - دبعل الشرقية - مسجد ب</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/June/مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-طرق-1-بطرم</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طرق: 1- بطرماز- بيت حاويك / 2- قرحيا - دبعل الشرقية - مسجد بيت حاويك / 3- السفيرة - حوارة - بيت حاويك / 4- بطرماز- دبعل الغربية في قضاء المنية الضنية.
+مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طرق: 1- بطرماز- بيت حاويك / 2- قرحيا - دبعل الشرقية - مسجد بيت حاويك / 3- السفيرة - حوارة - بيت حاويك / 4- بطرماز- دبعل الغربية في قضاء المنية الضنية.
+دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-4-طرق-في-قضاء-المنيه-الضنيه.pdf</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:33:08.368476+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق: فاریا - سد شبروح - حراجل - نبع المغارة - کفرذبیان - ط</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/June/مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-طريق-فاریا</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق: فاریا - سد شبروح - حراجل - نبع المغارة - کفرذبیان - طریق الملعب في قضاء كسروان
+مناقصة عمومية لتلزيم أشغال تأهيل وصيانة طريق: فاریا - سد شبروح - حراجل - نبع المغارة - کفرذبیان - طریق الملعب في قضاء كسروان
+دعوة-للاعلان-عن-مناقصة-عمومية-لتلزيم-اشغال-تاهيل-وصيانة-طريق-في-قضاء-كسروان.pdf</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:33:10.570773+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>مناقصة لأشغال تأهيل وصيانة طرق1- الحازمية - عالية - ضهر البيدر 2 - ضهر البيدر -شتورا- المصنع 3 -</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/June/مناقصة-لاشغال-تاهيل-وصيانة-طرق1-الحازمية-عالية-ضهر</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>مناقصة لأشغال تأهيل وصيانة طرق1- الحازمية - عالية - ضهر البيدر 2 - ضهر البيدر -شتورا- المصنع 3 - المصنع - راشيا-كفرشيما - مرج الزهور
+مناقصة لأشغال تأهيل وصيانة طرق1- الحازمية - عالية - ضهر البيدر 2 - ضهر البيدر -شتورا- المصنع 3 - المصنع - راشيا-كفرشيما - مرج الزهور
+اعلان-الملتزم-الموقت-لاشغال-تاهيل-وصيانة-3-طرق.pdf</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:33:14.872871+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>مناقصة لأشغال تأهيل وصيانة اتوستراد الزهراني- النبطية -كفرتبنيت</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/June/مناقصة-لاشغال-تاهيل-وصيانة-اتوستراد-الزهراني-النبط</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>26 حزيران 2024 مناقصة لأشغال تأهيل وصيانة اتوستراد الزهراني- النبطية -كفرتبنيت مناقصة لأشغال تأهيل وصيانة اتوستراد الزهراني- النبطية -كفرتبنيت اعلان-الملتزم-الموقت-لاشغال-تاهيل-وصيانة-اوتوستراد-الزهراني-النبطيه-كفرتبنيت.pdf</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:33:16.967869+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>إعلان الملتزم المؤقت لأشغال تأهيل وصيانة الطريق الدولي من نهر البارد الى الحدود السورية وتحديد فترة</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/June/اعلان-الملتزم-الموقت-لاشغال-تاهيل-وصيانة-الطريق-ال</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>إعلان الملتزم المؤقت لأشغال تأهيل وصيانة الطريق الدولي من نهر البارد الى الحدود السورية وتحديد فترة التجميد
+إعلان الملتزم المؤقت لأشغال تأهيل وصيانة الطريق الدولي من نهر البارد الى الحدود السورية
+وتحديد فترة التجميد
+اعلان-الملتزم-الموقت-لاشغال-تاهيل-وصيانة-طريق-الدولي-من-نهر-البارد-الى-الحدود-السورية.pdf</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:33:19.194872+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>إعلان الملتزم المؤقت لأشغال تأهيل وصيانة طريق شتورا- زحلة- بعلبك- القاع- الحدود السورية وتحديد فترة</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/June/اعلان-الملتزم-الموقت-لاشغال-تاهيل-وصيانة-طريق-شتور</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>إعلان الملتزم المؤقت لأشغال تأهيل وصيانة طريق شتورا- زحلة- بعلبك- القاع- الحدود السورية وتحديد فترة التجميد
+إعلان الملتزم المؤقت لأشغال تأهيل وصيانة طريق شتورا- زحلة- بعلبك- القاع- الحدود السورية
+وتحديد فترة التجميد
+اعلان-الملتزم-الموقت-لاشغال-تاهيل-وصيانة-طريق-شتورا-زحلة-بعلبك-القاع-الحدود-السورية.pdf</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:33:21.330405+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>إعلان الملتزم المؤقت لأشغال تأهيل وصيانة الأوتوستراد الساحلي: نهر إبراهيم – المدفون وتحديد فترة الت</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/June/اعلان-الملتزم-الموقت-لاشغال-تاهيل-وصيانة-الاوتوستر</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>إعلان الملتزم المؤقت لأشغال تأهيل وصيانة الأوتوستراد الساحلي: نهر إبراهيم – المدفون وتحديد فترة التجميد
+إعلان الملتزم المؤقت لأشغال تأهيل وصيانة الأوتوستراد الساحلي: نهر إبراهيم – المدفون
+وتحديد فترة التجميد
+اعلان-الملتزم-الموقت-لاشغال-تاهيل-وصيانة-الاوتوستراد-الساحلي-نهر-ابراهيم-المدفون.pdf</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:33:23.415177+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>إعلان الملتزم المؤقت لأشغال تأهيل وصيانة أوتوستراد صيدا - الزهراني- برج رحال وتحديد فترة التجميد</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/June/اعلان-الملتزم-الموقت-لاشغال-تاهيل-وصيانة-اوتوستراد</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>إعلان الملتزم المؤقت لأشغال تأهيل وصيانة أوتوستراد صيدا - الزهراني- برج رحال وتحديد فترة التجميد
+إعلان الملتزم المؤقت لأشغال تأهيل وصيانة أوتوستراد صيدا - الزهراني- برج رحال
+وتحديد فترة التجميد
+اعلان-الملتزم-الموقت-لاشغال-تاهيل-وصيانة-اوتوستراد-صيدا-الزهراني-برج-رحال.pdf</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:33:25.522367+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>اعلان الملتزم المؤقت لأشغال تأهيل وصيانة طريق رويسة البلوط - رأس المتن - الدليبة - العربانية -</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/June/اعلان-الملتزم-الموقت-لاشغال -تاهيل-وصيانة-طريق-روي</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>اعلان الملتزم المؤقت لأشغال تأهيل وصيانة طريق رويسة البلوط - رأس المتن - الدليبة - العربانية - بعبدات - بزبدين - قرنايل في قضاء بعبدا
+اعلان الملتزم المؤقت لأشغال  تأهيل وصيانة طريق رويسة البلوط - رأس المتن - الدليبة - العربانية - بعبدات - بزبدين - قرنايل في قضاء بعبدا 
+اعلان-الملتزم-الموقت-لاشغال-تاهيل-وصيانة-طريق-رويسة-البلوط-راس-المتن-الدليبة-العربانية-بعبدات-بزب-(1).pdf</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:33:27.628225+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>اعلان الملتزم المؤقت لأشغال تأهيل وصيانة طريق صليما العربانية - بعبدا و تحديد فترة التجميد</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/June/اعلان-الملتزم-الموقت-لاشغال-تاهيل-وصيانة-طريق-صليم</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>اعلان الملتزم المؤقت لأشغال تأهيل وصيانة طريق صليما العربانية - بعبدا و تحديد فترة التجميد
+ اعلان الملتزم المؤقت لأشغال تأهيل وصيانة طريق صليما العربانية - بعبدا و تحديد فترة التجميد 
+اعلان-الملتزم-الموقت-لاشغال-تاهيل-وصيانة-طريق-صليما-العربانية-بعبدا-pd.pdf</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:33:29.775713+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>اعلان الملتزم المؤقت لأشغال تأهيل وصيانة طريق قرنايل-جورة أرصون في قضاء بعبدا و تحديد فترة التج</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/June/اعلان-الملتزم-الموقت-لاشغال-تاهيل-وصيانة-طريق-قرنا</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>اعلان الملتزم المؤقت لأشغال تأهيل وصيانة طريق قرنايل-جورة أرصون في قضاء بعبدا و تحديد فترة التجميد
+ اعلان الملتزم المؤقت لأشغال تأهيل وصيانة طريق قرنايل-جورة أرصون في قضاء بعبدا و تحديد فترة التجميد
+اعلان-الملتزم-الموقت-لاشغال-تاهيل-وصيانة-طريق-قرنايل-جورة-ارصون(بعبدا).pdf</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:33:31.883874+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>اعلان الملتزم المؤقت لأشغال تأهيل وصيانة طريق قعقعية الجسر-فرون في قضاء النبطية و تحديد فترة الت</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(1)/2024/June/اعلان-الملتزم-الموقت-لاشغال-تاهيل-وصيانة-طريق-قعقع</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>اعلان الملتزم المؤقت لأشغال تأهيل وصيانة طريق قعقعية الجسر-فرون في قضاء النبطية و تحديد فترة التجميد
+ اعلان الملتزم المؤقت لأشغال تأهيل وصيانة طريق قعقعية الجسر-فرون في قضاء النبطية و تحديد فترة التجميد
+اعلان-الملتزم-الموقت-لاشغال-تاهيل-وصيانة-طريق-قعقعية-الجسر-فرون(النبطية).pdf</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:33:33.977242+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>قرار رقم 625/1</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(2)/2023/December/قرار-رقم-625-1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>18 كانون الأول 2023 قرار رقم 625/1 اعلان الملتزم المؤقت للمناقصة العمومية لأشغال مشروع ترميم على بعض الطرق الرئيسية، الثانوية، المحلية والداخلية في أقضية بعلبك، كسروان وجبيل وتحديد فترة التجميد اعلان-الملتزم-الموقت-للمناقصة-العمومية-لاشغال-مشروع-ترميم-على-بعض-الطرق-في-اقضية-بعلبك-كسروان-وجب.pdf</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:33:38.421797+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>قرار رقم 624/1</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(2)/2023/December/قرار-رقم-624-1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>قرار رقم 624/1
+اعلان الملتزم المؤقت للمناقصة العمومية لتلزيم شراء كميات من الملح المطلوبة للإستعمال على الطرقات الجبلية أثناء فصل الشتاء وتحديد فترة التجميد
+اعلان-الملتزم-الموقت-للمناقصة-العمومية-لتلزيم-شراء-كميات-من-الملح-للاستعمال-على-الطرقات-الجبلية-(1).pdf</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:33:40.675129+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>قرار إلغاء إجراءات ونتيجة إعلان الملتزم المؤقت للمزايدة العمومية لتلزيم إستثمار وتشغيل مواقف السيارا</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(2)/2023/December/قرار-الغاء-اجراءات-ونتيجة-اعلان-الملتزم-الموقت-للم</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>قرار إلغاء إجراءات ونتيجة إعلان الملتزم المؤقت للمزايدة العمومية لتلزيم إستثمار وتشغيل مواقف السيارات في مطار رفيق الحريري الدولي- بيروت
+قرار إلغاء إجراءات ونتيجة إعلان الملتزم المؤقت للمزايدة العمومية لتلزيم إستثمار وتشغيل مواقف السيارات في مطار رفيق الحريري الدولي- بيروت
+كتاب-وزير-الغاء-اجراءات-ونتيجة-اعلان-الملتزم-الموقت-للمزايدة-العمومية-لتلزيم-وتشغيل-مواقف-السيا-(1).pdf</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:33:42.991314+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>قرار رقم 561 /1 قبول العرض الوحيد المقبول في المناقصة العمومية لتلزيم تأمين آليات الادارة العاملة ف</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(2)/2023/November/قرار-رقم-561-1-قبول-العرض-الوحيد-المقبول-في-المناق</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>قرار رقم 561 /1 قبول العرض الوحيد المقبول في المناقصة العمومية لتلزيم تأمين آليات الادارة العاملة في ورش رفع الثلوج
+قرار رقم  561 /1 قبول العرض الوحيد المقبول في المناقصة العمومية لتلزيم تأمين آليات الادارة العاملة في ورش رفع الثلوج
+قبول-العرض-الوحيد-المقبول-في-المناقصة-العمومية-لتلزيم-تامين-اليات-الادارة-العاملة-في-ورش-رفع-الثل.pdf</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:33:45.123030+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>الملتزم المؤقت للمزايدة العمومية لتلزيم استثمار وتشغيل مواقف السيارات في مطار رفيق الحريري الدولي</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(2)/2023/November/اعلان-الملتزم-الموقت-للمزايدة-العمومية-لتلزيم-استث</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>الملتزم المؤقت للمزايدة العمومية لتلزيم استثمار وتشغيل مواقف السيارات في مطار رفيق الحريري الدولي
+قرار رقم 506  /1 اعلان الملتزم المؤقت للمزايدة العمومية لتلزيم استثمار وتشغيل مواقف السيارات في مطار رفيق الحريري الدولي- بيروت وتحديد فترة التجميد
+قرار-اعلان-الملتزم-الموقت-للمزايدة-العمومية-لتلزيم-استثمار-وتشغيل-مواقف-السيارات-في-مطار-رفيق-الحريري-الدولي.pdf</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:33:47.223163+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>الملتزم المؤقت لمناقصة تلزيم مشروع تنظيف وتأهيل شبكات تصريف مياه الأمطار والمجاري الصحية في الحازمي</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(2)/2023/November/علان-الملتزم-الموقت-لمناقصة-تلزيم-مشروع-تنظيف-وتاه</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>الملتزم المؤقت لمناقصة تلزيم مشروع تنظيف وتأهيل شبكات تصريف مياه الأمطار والمجاري الصحية في الحازمية
+قرار رقم 504/1 اعلان الملتزم المؤقت لمناقصة تلزيم مشروع تنظيف وتأهيل شبكات تصريف مياه الأمطار والمجاري الصحية في الحازمية- شتورة- المصنع/ المصنع- راشيا- مرج الزهور وتحديد فترة التجميد
+قرار-اعلان-الملتزم-الموقت-لمناقصة-تلزيم-مشروع-تنظيف-وتاهيل-شبكات-تصريف-مياه-الامطار-والمجاري-الصح.pdf</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:33:49.452830+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>الملتزم المؤقت للمناقصة العمومية لتقديم وتركيب قطع غيار لزوم صيانة وتشغيل آليات رفع الثلوج</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(2)/2023/November/اعلان-الملتزم-الموقت-للمناقصة-العمومية-لتقديم-وترك</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>الملتزم المؤقت للمناقصة العمومية لتقديم وتركيب قطع غيار لزوم صيانة وتشغيل آليات رفع الثلوج
+قرار رقم503  /1 اعلان الملتزم المؤقت للمناقصة العمومية لتقديم وتركيب قطع غيار لزوم صيانة وتشغيل آليات رفع الثلوج العائدة للمديرية العامة للطرق والمباني والمديريات الاقليمية وتحديد فترة التجميد
+قرار-اعلان-الملتزم-الموقت-للمناقصة-العمومية-لتقديم-وتركيب-قطع-غيار-لزوم-صيانة-وتشغيل-اليات-رفع-ال.pdf</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:33:51.520911+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>الملتزم المؤقت للمناقصة العمومية لتأمين شراء زيوت، فلاتر، بطاريات، سلاسل معدنية وسكاكين فولاذية</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(2)/2023/November/اعلان-الملتزم-الموقت-للمناقصة-العمومية-لتامين-شراء</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>الملتزم المؤقت للمناقصة العمومية لتأمين شراء زيوت، فلاتر، بطاريات، سلاسل معدنية وسكاكين فولاذية
+قرار رقم 502/1 اعلان الملتزم المؤقت للمناقصة العمومية لتأمين شراء زيوت، فلاتر، بطاريات، سلاسل معدنية وسكاكين فولاذية لآليات الادارة العاملة في ورش رفع الثلوج وتحديد فترة التجميد</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:33:54.346334+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>الملتزم المؤقت للمناقصة العمومية لأشغال تأهيل طريق كفرشيما</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(2)/2023/November/1اعلان-الملتزم-الموقت-للمناقصة-العمومية-لاشغال-تاه</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>الملتزم المؤقت للمناقصة العمومية لأشغال تأهيل طريق كفرشيما
+قرار رقم 501 /1اعلان الملتزم المؤقت للمناقصة العمومية لأشغال تأهيل طريق كفرشيما- ساحة كنيسة مار بطرس وبولس/قضاء بعبدا وتحديد فترة التجميد
+قرار-اعلان-الملتزم-الموقت-للمناقصة-العمومية-لاشغال-تاهيل-طريق-كفرشيما-ساحة-كنيسة-مار-بطرس-وبولس.pdf</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:33:56.588336+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>قرار 1/455قبول العرض الوحيد المقبول لأشغال ترميم شبكة الطرق في قضاء بعلبك</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(2)/2023/October/قرار-1-455قبول-العرض-الوحيد-المقبول-لاشغال-ترميم-ش</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>قرار 1/455قبول العرض الوحيد المقبول لأشغال ترميم شبكة الطرق في قضاء بعلبك
+قرار رقم 455/1 قبول العرض الوحيد المقبول في المناقصة العمومية لأشغال ترميم شبكة الطرق في قضاء بعلبك
+قرار-قبول-العرض-الوحيد-المقبول-في-المناقصة-العمومية-لاشغال-ترميم-شبكة-الطرق-في-قضاء-بعلبك.pdf</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:33:58.867256+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>قرار 1033/1 لإلغاء القرار رقم 960/1/2022</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(2)/2022/November/قرار-1033-1-لالغاء-القرار-رقم-960-1-2022</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>قرار 1033/1 لإلغاء القرار رقم 960/1/2022
+إلغاء الفرار رقم 960/1/2022 القاضي بإعتبار شركة باك - دوتي فري الملتزم المؤقت للمزايدة العلنية لإدارة و إستثمار مساحات مخصصة للبيع بالمفرق في
+السوق-الحرة.pdf مبنى الركاب الحالي و مبنى الطيران العام في مطار رفيق الحريري الدولي - بيروت</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:34:03.308098+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>اعتبار شركة باك الملتزم لمؤقت للمزايدة العلنية</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>http://www.mopw.gov.lb/media/news-(2)/2022/October/اعتبار-شركة-باك-الملتزم-لموقت-للمزايدة-العلنية</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2022-01-01</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>01 تشرين الأول 2022 اعتبار شركة باك الملتزم لمؤقت للمزايدة العلنية اعتبار شركة - باك دوتي فري - الملتزم المؤقت للمزايدة العلنية لإدارة واستثمار مساحات مخصصة للبيع بالمفرق في مبنى محطة الركاب الحالي ومبنى الطيران العام في مطار رفيق الحريري الدولي قرار-اعتبار-شركة-باك-ديوتي-فري-الملتزم-الموقت-للمزايدة-العلنية-للسوق-الحرة.pdf</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:34:05.563309+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
